--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_029.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_029.xlsx
@@ -41,22 +41,22 @@
     <t>Decreto del Tribunale</t>
   </si>
   <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Allegato aggiuntivo</t>
+  </si>
+  <si>
+    <t>Formula</t>
+  </si>
+  <si>
+    <t>999.9.9</t>
+  </si>
+  <si>
     <t>SI</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Allegato aggiuntivo</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>Formula</t>
-  </si>
-  <si>
-    <t>999.9.9</t>
   </si>
   <si>
     <t>Si puo' ignorare la sezione per</t>
@@ -577,7 +577,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>10</v>
@@ -594,13 +594,13 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>10</v>
@@ -646,7 +646,7 @@
         <v>17</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>18</v>
@@ -669,7 +669,7 @@
         <v>21</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>18</v>
@@ -692,7 +692,7 @@
         <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>18</v>
@@ -715,7 +715,7 @@
         <v>25</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>18</v>
@@ -738,7 +738,7 @@
         <v>28</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>29</v>
@@ -761,7 +761,7 @@
         <v>31</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>29</v>
@@ -784,7 +784,7 @@
         <v>33</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>29</v>
@@ -807,7 +807,7 @@
         <v>35</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>29</v>
@@ -830,7 +830,7 @@
         <v>38</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>39</v>
@@ -853,7 +853,7 @@
         <v>41</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>39</v>
@@ -876,7 +876,7 @@
         <v>43</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>39</v>
@@ -899,7 +899,7 @@
         <v>45</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>39</v>
@@ -922,7 +922,7 @@
         <v>47</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>39</v>
@@ -945,7 +945,7 @@
         <v>49</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>39</v>
@@ -968,7 +968,7 @@
         <v>51</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>39</v>
@@ -991,7 +991,7 @@
         <v>53</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>39</v>
@@ -1014,7 +1014,7 @@
         <v>55</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>39</v>
@@ -1037,7 +1037,7 @@
         <v>57</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>39</v>
@@ -1060,7 +1060,7 @@
         <v>59</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>39</v>
@@ -1083,7 +1083,7 @@
         <v>61</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>39</v>
@@ -1106,7 +1106,7 @@
         <v>63</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>39</v>
@@ -1129,7 +1129,7 @@
         <v>65</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>39</v>
@@ -1152,7 +1152,7 @@
         <v>67</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>39</v>
@@ -1175,7 +1175,7 @@
         <v>69</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>39</v>
@@ -1198,7 +1198,7 @@
         <v>71</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>39</v>
@@ -1221,7 +1221,7 @@
         <v>73</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>39</v>
@@ -1244,7 +1244,7 @@
         <v>75</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>39</v>
@@ -1267,7 +1267,7 @@
         <v>77</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>39</v>
@@ -1290,7 +1290,7 @@
         <v>79</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>39</v>
@@ -1313,7 +1313,7 @@
         <v>81</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>39</v>
@@ -1336,7 +1336,7 @@
         <v>83</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>39</v>
@@ -1359,7 +1359,7 @@
         <v>85</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>39</v>
@@ -1382,7 +1382,7 @@
         <v>87</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>39</v>
@@ -1405,7 +1405,7 @@
         <v>89</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>39</v>
@@ -1428,7 +1428,7 @@
         <v>91</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>39</v>
@@ -1451,7 +1451,7 @@
         <v>93</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>39</v>
@@ -1474,7 +1474,7 @@
         <v>95</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>39</v>
@@ -1497,7 +1497,7 @@
         <v>97</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>39</v>
@@ -1520,7 +1520,7 @@
         <v>99</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>39</v>
@@ -1543,7 +1543,7 @@
         <v>101</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>39</v>
@@ -1566,7 +1566,7 @@
         <v>38</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>104</v>
@@ -1589,7 +1589,7 @@
         <v>41</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>104</v>
@@ -1612,7 +1612,7 @@
         <v>43</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>104</v>
@@ -1635,7 +1635,7 @@
         <v>45</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>104</v>
@@ -1658,7 +1658,7 @@
         <v>47</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>104</v>
@@ -1681,7 +1681,7 @@
         <v>49</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>104</v>
@@ -1704,7 +1704,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>104</v>
@@ -1727,7 +1727,7 @@
         <v>53</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>104</v>
@@ -1750,7 +1750,7 @@
         <v>55</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>104</v>
@@ -1773,7 +1773,7 @@
         <v>57</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>104</v>
@@ -1796,7 +1796,7 @@
         <v>59</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>104</v>
@@ -1819,7 +1819,7 @@
         <v>61</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>104</v>
@@ -1842,7 +1842,7 @@
         <v>63</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>104</v>
@@ -1865,7 +1865,7 @@
         <v>65</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>104</v>
@@ -1888,7 +1888,7 @@
         <v>67</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>104</v>
@@ -1911,7 +1911,7 @@
         <v>69</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>104</v>
@@ -1934,7 +1934,7 @@
         <v>71</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>104</v>
@@ -1957,7 +1957,7 @@
         <v>73</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>104</v>
@@ -1980,7 +1980,7 @@
         <v>75</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>104</v>
@@ -2003,7 +2003,7 @@
         <v>77</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>104</v>
@@ -2026,7 +2026,7 @@
         <v>79</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>104</v>
@@ -2049,7 +2049,7 @@
         <v>81</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>104</v>
@@ -2072,7 +2072,7 @@
         <v>83</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>104</v>
@@ -2095,7 +2095,7 @@
         <v>85</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>104</v>
@@ -2118,7 +2118,7 @@
         <v>87</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>104</v>
@@ -2141,7 +2141,7 @@
         <v>89</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>104</v>
@@ -2164,7 +2164,7 @@
         <v>91</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>104</v>
@@ -2187,7 +2187,7 @@
         <v>105</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>104</v>
@@ -2210,7 +2210,7 @@
         <v>95</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>104</v>
@@ -2233,7 +2233,7 @@
         <v>97</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>104</v>
@@ -2256,7 +2256,7 @@
         <v>99</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>104</v>
@@ -2279,7 +2279,7 @@
         <v>101</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>104</v>
@@ -2302,7 +2302,7 @@
         <v>106</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>104</v>
@@ -2325,7 +2325,7 @@
         <v>38</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>109</v>
@@ -2348,7 +2348,7 @@
         <v>41</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>109</v>
@@ -2371,7 +2371,7 @@
         <v>43</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>109</v>
@@ -2394,7 +2394,7 @@
         <v>45</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>109</v>
@@ -2417,7 +2417,7 @@
         <v>47</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>109</v>
@@ -2440,7 +2440,7 @@
         <v>49</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>109</v>
@@ -2463,7 +2463,7 @@
         <v>51</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>109</v>
@@ -2486,7 +2486,7 @@
         <v>53</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>109</v>
@@ -2509,7 +2509,7 @@
         <v>55</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>109</v>
@@ -2532,7 +2532,7 @@
         <v>57</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>109</v>
@@ -2555,7 +2555,7 @@
         <v>59</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>109</v>
@@ -2578,7 +2578,7 @@
         <v>61</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>109</v>
@@ -2601,7 +2601,7 @@
         <v>63</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>109</v>
@@ -2624,7 +2624,7 @@
         <v>65</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>109</v>
@@ -2647,7 +2647,7 @@
         <v>67</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>109</v>
@@ -2670,7 +2670,7 @@
         <v>69</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>109</v>
@@ -2693,7 +2693,7 @@
         <v>71</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>109</v>
@@ -2716,7 +2716,7 @@
         <v>73</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>109</v>
@@ -2739,7 +2739,7 @@
         <v>75</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>109</v>
@@ -2762,7 +2762,7 @@
         <v>77</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>109</v>
@@ -2785,7 +2785,7 @@
         <v>79</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>109</v>
@@ -2808,7 +2808,7 @@
         <v>81</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>109</v>
@@ -2831,7 +2831,7 @@
         <v>83</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>109</v>
@@ -2854,7 +2854,7 @@
         <v>85</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>109</v>
@@ -2877,7 +2877,7 @@
         <v>87</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>109</v>
@@ -2900,7 +2900,7 @@
         <v>89</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>109</v>
@@ -2923,7 +2923,7 @@
         <v>91</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>109</v>
@@ -2946,7 +2946,7 @@
         <v>105</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>109</v>
@@ -2969,7 +2969,7 @@
         <v>95</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>109</v>
@@ -2992,7 +2992,7 @@
         <v>97</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>109</v>
@@ -3015,7 +3015,7 @@
         <v>99</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>109</v>
@@ -3038,7 +3038,7 @@
         <v>101</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>109</v>
@@ -3061,7 +3061,7 @@
         <v>106</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>109</v>
@@ -3084,7 +3084,7 @@
         <v>111</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>112</v>
@@ -3107,7 +3107,7 @@
         <v>114</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>112</v>
@@ -3130,7 +3130,7 @@
         <v>116</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>112</v>
@@ -3153,7 +3153,7 @@
         <v>118</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>112</v>
@@ -3176,7 +3176,7 @@
         <v>120</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>112</v>
@@ -3199,7 +3199,7 @@
         <v>122</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>112</v>
@@ -3222,7 +3222,7 @@
         <v>124</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>112</v>
@@ -3245,7 +3245,7 @@
         <v>126</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>112</v>
@@ -3268,7 +3268,7 @@
         <v>128</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>112</v>
@@ -3291,7 +3291,7 @@
         <v>65</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>112</v>
@@ -3314,7 +3314,7 @@
         <v>38</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>132</v>
@@ -3337,7 +3337,7 @@
         <v>41</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>132</v>
@@ -3360,7 +3360,7 @@
         <v>43</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>132</v>
@@ -3383,7 +3383,7 @@
         <v>45</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>132</v>
@@ -3406,7 +3406,7 @@
         <v>47</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>132</v>
@@ -3429,7 +3429,7 @@
         <v>49</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>132</v>
@@ -3452,7 +3452,7 @@
         <v>51</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>132</v>
@@ -3475,7 +3475,7 @@
         <v>53</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>132</v>
@@ -3498,7 +3498,7 @@
         <v>55</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>132</v>
@@ -3521,7 +3521,7 @@
         <v>57</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>132</v>
@@ -3544,7 +3544,7 @@
         <v>59</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>132</v>
@@ -3567,7 +3567,7 @@
         <v>61</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>132</v>
@@ -3590,7 +3590,7 @@
         <v>63</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>132</v>
@@ -3613,7 +3613,7 @@
         <v>65</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>132</v>
@@ -3636,7 +3636,7 @@
         <v>67</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>132</v>
@@ -3659,7 +3659,7 @@
         <v>69</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>132</v>
@@ -3682,7 +3682,7 @@
         <v>71</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>132</v>
@@ -3705,7 +3705,7 @@
         <v>73</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>132</v>
@@ -3728,7 +3728,7 @@
         <v>75</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>132</v>
@@ -3751,7 +3751,7 @@
         <v>77</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>132</v>
@@ -3774,7 +3774,7 @@
         <v>79</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>132</v>
@@ -3797,7 +3797,7 @@
         <v>81</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>132</v>
@@ -3820,7 +3820,7 @@
         <v>83</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>132</v>
@@ -3843,7 +3843,7 @@
         <v>85</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>132</v>
@@ -3866,7 +3866,7 @@
         <v>87</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>132</v>
@@ -3889,7 +3889,7 @@
         <v>89</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>132</v>
@@ -3912,7 +3912,7 @@
         <v>91</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>132</v>
@@ -3935,7 +3935,7 @@
         <v>93</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>132</v>
@@ -3958,7 +3958,7 @@
         <v>95</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>132</v>
@@ -3981,7 +3981,7 @@
         <v>97</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>132</v>
@@ -4004,7 +4004,7 @@
         <v>99</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>132</v>
@@ -4027,7 +4027,7 @@
         <v>101</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>132</v>
@@ -4050,7 +4050,7 @@
         <v>116</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>134</v>
@@ -4073,7 +4073,7 @@
         <v>118</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>134</v>
@@ -4096,7 +4096,7 @@
         <v>120</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>134</v>
@@ -4119,7 +4119,7 @@
         <v>122</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>134</v>
@@ -4142,7 +4142,7 @@
         <v>124</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>134</v>
@@ -4165,7 +4165,7 @@
         <v>126</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>134</v>
@@ -4188,7 +4188,7 @@
         <v>128</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>134</v>
@@ -4211,7 +4211,7 @@
         <v>136</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>134</v>
@@ -4234,7 +4234,7 @@
         <v>138</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>134</v>
@@ -4257,7 +4257,7 @@
         <v>140</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>134</v>
@@ -4280,7 +4280,7 @@
         <v>141</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>18</v>
@@ -4303,7 +4303,7 @@
         <v>144</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>145</v>
